--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -64,14 +64,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0E0"/>
-        <bgColor rgb="00FFE0E0"/>
+        <fgColor rgb="00E0FFE0"/>
+        <bgColor rgb="00E0FFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0FFE0"/>
-        <bgColor rgb="00E0FFE0"/>
+        <fgColor rgb="00FFE0E0"/>
+        <bgColor rgb="00FFE0E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: https://cn.investing.com/commodities/us-coffee-c-historical-data  |  抓取时间: 2026-06-18 11:51:50</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-06-29 05:34:35</t>
         </is>
       </c>
     </row>
@@ -544,819 +544,1559 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>276.20</t>
+          <t>265.60</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>280.00</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>280.00</t>
+          <t>274.60</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>265.30</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>260.60</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>266.40</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>269.40</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>-2.19%</t>
+          <t>17189</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>268.30</t>
+          <t>259.20</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>270.00</t>
+          <t>260.70</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>262.30</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>264.20</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>-0.68%</t>
+          <t>12712</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>273.40</t>
+          <t>253.10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>268.80</t>
+          <t>261.10</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>274.30</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>266.50</t>
+          <t>252.40</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>274.80</t>
+          <t>254.10</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>270.70</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>19034</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>274.00</t>
+          <t>246.50</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>270.40</t>
+          <t>248.00</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>249.20</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>243.30</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>245.90</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>246.00</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>276.80</t>
+          <t>250.85</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>268.80</t>
+          <t>244.30</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>244.40</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>271.00</t>
+          <t>245.60</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>278.40</t>
+          <t>249.15</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>242.70</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>-0.61%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>265.60</t>
+          <t>248.40</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>245.20</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>274.60</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>265.30</t>
+          <t>244.70</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>+1.64%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>260.60</t>
+          <t>253.95</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>247.50</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>269.40</t>
+          <t>255.50</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>247.50</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>19762</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>+2.23%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>259.20</t>
+          <t>257.20</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>260.70</t>
+          <t>255.00</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>262.30</t>
+          <t>257.95</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>252.90</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>+1.28%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>253.10</t>
+          <t>262.95</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>261.10</t>
+          <t>256.20</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>261.70</t>
+          <t>265.10</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>252.40</t>
+          <t>256.20</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>+2.24%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>277.25</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>263.95</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>254.10</t>
+          <t>279.20</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>260.40</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>+5.44%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>246.50</t>
+          <t>277.85</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>248.00</t>
+          <t>277.50</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>249.20</t>
+          <t>279.95</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>243.30</t>
+          <t>271.70</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.22%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>275.10</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>242.00</t>
+          <t>279.75</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>246.10</t>
+          <t>285.75</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>240.00</t>
+          <t>270.50</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>-1.97%</t>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026年6月9日</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>240.90</t>
+          <t>277.00</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>272.00</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>244.65</t>
+          <t>278.45</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>238.85</t>
+          <t>269.80</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>26.41K</t>
+          <t>279</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.69%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>244.60</t>
+          <t>287.95</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.15</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>246.00</t>
+          <t>290.95</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>241.00</t>
+          <t>273.15</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>+3.95%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>291.55</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>290.00</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>251.70</t>
+          <t>298.80</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>243.60</t>
+          <t>288.00</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>+2.31%</t>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>+1.25%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>253.40</t>
+          <t>288.80</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>295.35</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>295.35</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>282.00</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>-0.94%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>259.20</t>
+          <t>286.75</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>252.40</t>
+          <t>285.30</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>261.10</t>
+          <t>285.30</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>285.30</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>-0.71%</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>272.80</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>259.60</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>256.40</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>2026年5月19日</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>270.15</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>266.4</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>270.95</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>262.85</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>15.13K</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月20日</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>268.3</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>270.0</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>272.0</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>264.2</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月21日</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>273.4</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>268.8</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>274.3</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>266.5</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月22日</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>272.35</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>273.85</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>274.8</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>270.7</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月26日</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>274.0</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>270.4</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>275.25</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>267.15</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月27日</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>269.85</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>273.85</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>276.8</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>268.8</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月28日</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>274.25</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>271.0</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>278.4</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>270.95</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月29日</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>265.6</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>273.25</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>274.6</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>265.3</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月10日</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>244.6</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>241.55</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>246.0</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>241.0</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>26.81K</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>+1.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月11日</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>250.25</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>243.65</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>251.7</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>243.6</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>25.64K</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>+2.31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月12日</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>253.4</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>251.15</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>254.35</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>249.25</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>21.91K</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>+1.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月15日</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>259.2</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>252.4</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>261.1</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>252.25</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>23.18K</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>+2.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月16日</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>272.8</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>259.6</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>274.95</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>256.4</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>2026年6月17日</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>271.90</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>273.00</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>274.70</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>271.9</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>273.0</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>274.7</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>266.45</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>26.40K</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>-0.33%</t>
         </is>
       </c>
     </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月1日</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>260.6</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>265.85</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>269.4</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>259.55</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>17.19K</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>-1.88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月2日</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>259.2</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>260.7</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>262.3</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>258.15</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>12.71K</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>-0.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月3日</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>253.1</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>261.1</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>261.7</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>252.4</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>19.79K</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>-2.35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月4日</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>247.15</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>252.75</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>254.1</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>246.85</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>19.03K</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>-2.35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月5日</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>246.5</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>249.2</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>243.3</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>26.62K</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月9日</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>240.9</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>244.65</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>238.85</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>26.41K</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G26"/>
+  <autoFilter ref="A4:G46"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-06-29 05:34:35</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-06-30 05:00:53</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>265.60</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>274.60</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>265.30</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -609,9 +609,9 @@
           <t>17189</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>-1.88%</t>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1284,698 +1284,698 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>291.10</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>291.10</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>291.10</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>291.10</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>+1.52%</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -1987,116 +1987,153 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G46"/>
+  <autoFilter ref="A4:G47"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-06-30 05:00:53</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-01 05:20:15</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -1321,698 +1321,698 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>311.20</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.10</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>+6.90%</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -2024,116 +2024,153 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G47"/>
+  <autoFilter ref="A4:G48"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-01 05:20:15</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-02 04:56:14</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>260.60</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>269.40</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -646,9 +646,9 @@
           <t>12712</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>-0.54%</t>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1358,698 +1358,698 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>324.30</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>310.00</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>326.25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>310.00</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>+4.21%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -2061,116 +2061,153 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G48"/>
+  <autoFilter ref="A4:G49"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-02 04:56:14</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-03 04:40:22</t>
         </is>
       </c>
     </row>
@@ -623,17 +623,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>259.20</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>260.70</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>262.30</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -683,9 +683,9 @@
           <t>19790</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>-2.35%</t>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1395,698 +1395,698 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>315.65</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>315.65</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>315.65</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>315.65</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.67%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -2098,116 +2098,153 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G49"/>
+  <autoFilter ref="A4:G50"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-03 04:40:22</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-04 04:33:40</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-04 04:33:40</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-05 04:54:54</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>253.10</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>261.10</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>261.70</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>252.40</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>254.10</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -757,9 +757,9 @@
           <t>26616</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>-0.26%</t>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1400,32 +1400,32 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>315.65</t>
+          <t>287.45</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>315.65</t>
+          <t>296.50</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>315.65</t>
+          <t>316.80</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>315.65</t>
+          <t>300.05</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-11.36%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-05 04:54:54</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-06 05:08:53</t>
         </is>
       </c>
     </row>
@@ -734,22 +734,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>246.50</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>248.00</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>249.20</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>243.30</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -794,9 +794,9 @@
           <t>22261</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1400,32 +1400,32 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>287.45</t>
+          <t>315.65</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>296.50</t>
+          <t>315.65</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>316.80</t>
+          <t>315.65</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>300.05</t>
+          <t>315.65</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>-11.36%</t>
+          <t>-2.67%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-06 05:08:53</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-07 04:50:32</t>
         </is>
       </c>
     </row>
@@ -1432,698 +1432,698 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>363.95</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>333.85</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>348.00</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>333.85</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>+15.30%</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -2135,116 +2135,153 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G50"/>
+  <autoFilter ref="A4:G51"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-07 04:50:32</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-08 04:12:36</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1469,698 +1469,698 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>331.60</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>331.60</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>331.60</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>331.60</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-8.89%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -2172,116 +2172,153 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G51"/>
+  <autoFilter ref="A4:G52"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-08 04:12:36</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-09 04:50:56</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>245.90</t>
+          <t>245.9</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>246.00</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>244.30</t>
+          <t>244.3</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -831,9 +831,9 @@
           <t>26801</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>-0.61%</t>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -1506,698 +1506,698 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>324.25</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>334.10</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>334.10</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>319.00</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.22%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -2209,116 +2209,153 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G52"/>
+  <autoFilter ref="A4:G53"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-09 04:50:56</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-10 04:49:27</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>244.40</t>
+          <t>244.4</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>245.60</t>
+          <t>245.6</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>242.70</t>
+          <t>242.7</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>+1.64%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -1543,698 +1543,698 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>356.95</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>356.95</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>356.95</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>356.95</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>+10.08%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -2246,116 +2246,153 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G53"/>
+  <autoFilter ref="A4:G54"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-10 04:49:27</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-11 04:11:13</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>248.40</t>
+          <t>248.4</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>245.20</t>
+          <t>245.2</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>244.70</t>
+          <t>244.7</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -1580,698 +1580,698 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-3.91%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -2283,116 +2283,153 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G54"/>
+  <autoFilter ref="A4:G55"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-11 04:11:13</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-12 04:23:24</t>
         </is>
       </c>
     </row>
@@ -887,17 +887,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>247.50</t>
+          <t>247.5</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>255.50</t>
+          <t>255.5</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>247.50</t>
+          <t>247.5</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1585,32 +1585,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>318.60</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>321.00</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>340.70</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>318.60</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>31069</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-10.74%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-12 04:23:24</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-13 04:29:29</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>257.20</t>
+          <t>257.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>255.00</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>252.90</t>
+          <t>252.9</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>+2.24%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1585,32 +1585,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>318.60</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>321.00</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>340.70</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>318.60</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>31069</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>-10.74%</t>
+          <t>-3.91%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-13 04:29:29</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-14 03:55:21</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -1617,698 +1617,698 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>330.50</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.90</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>340.25</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>321.50</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-3.64%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -2320,116 +2320,153 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G55"/>
+  <autoFilter ref="A4:G56"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-14 03:55:21</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-15 03:56:41</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1622,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>330.50</t>
+          <t>341.40</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>314.90</t>
+          <t>341.40</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>340.25</t>
+          <t>341.40</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>321.50</t>
+          <t>341.40</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1647,705 +1647,705 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>-0.47%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>327.00</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>309.45</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>352.40</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>322.85</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-4.22%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -2357,116 +2357,153 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G56"/>
+  <autoFilter ref="A4:G57"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-15 03:56:41</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-16 04:07:06</t>
         </is>
       </c>
     </row>
@@ -961,17 +961,17 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>256.20</t>
+          <t>256.2</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>265.10</t>
+          <t>265.1</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>256.20</t>
+          <t>256.2</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1659,730 +1659,730 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>327.00</t>
+          <t>337.20</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>309.45</t>
+          <t>335.00</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>352.40</t>
+          <t>335.00</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>322.85</t>
+          <t>335.00</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>-4.22%</t>
+          <t>-1.23%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>334.45</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>334.45</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>334.45</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>334.45</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.82%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -2394,116 +2394,153 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G57"/>
+  <autoFilter ref="A4:G58"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-16 04:07:06</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-17 03:58:11</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -1728,698 +1728,698 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>313.95</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>323.05</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>325.00</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>310.50</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-6.13%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -2431,116 +2431,153 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G58"/>
+  <autoFilter ref="A4:G59"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-17 03:58:11</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-18 03:53:02</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>279.20</t>
+          <t>279.2</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>260.40</t>
+          <t>260.4</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1733,22 +1733,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>313.95</t>
+          <t>321.30</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>323.05</t>
+          <t>321.30</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>325.00</t>
+          <t>321.30</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>310.50</t>
+          <t>321.30</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1758,705 +1758,705 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>-6.13%</t>
+          <t>-3.93%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>321.10</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>298.15</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>324.40</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>311.35</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.06%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -2468,116 +2468,153 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G59"/>
+  <autoFilter ref="A4:G60"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-18 03:53:02</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-19 04:20:04</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>277.50</t>
+          <t>277.5</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>271.70</t>
+          <t>271.7</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>275.10</t>
+          <t>275.1</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>270.50</t>
+          <t>270.5</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>321.10</t>
+          <t>304.70</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-5.17%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-19 04:20:04</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-20 04:34:09</t>
         </is>
       </c>
     </row>
@@ -1770,32 +1770,32 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>304.70</t>
+          <t>328.45</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>298.15</t>
+          <t>328.45</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>324.40</t>
+          <t>328.45</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>311.35</t>
+          <t>328.45</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>14662</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>+2.23%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-20 04:34:09</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-21 04:13:23</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -1802,698 +1802,698 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>334.40</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>328.45</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>335.25</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>328.45</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>+1.81%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -2505,116 +2505,153 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G60"/>
+  <autoFilter ref="A4:G61"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-21 04:13:23</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-22 04:15:08</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -1839,698 +1839,698 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>331.95</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>331.95</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>331.95</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>331.95</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.73%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -2542,116 +2542,153 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G61"/>
+  <autoFilter ref="A4:G62"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-22 04:15:08</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-23 04:13:44</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>277.00</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>269.80</t>
+          <t>269.8</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -1876,698 +1876,698 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>316.65</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>320.85</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>324.60</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>313.35</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-4.61%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -2579,116 +2579,153 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G62"/>
+  <autoFilter ref="A4:G63"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-23 04:13:44</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-24 04:12:31</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -1913,698 +1913,698 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>309.40</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>320.55</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>321.30</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>308.25</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.29%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -2616,116 +2616,153 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G63"/>
+  <autoFilter ref="A4:G64"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-24 04:12:31</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-25 04:07:37</t>
         </is>
       </c>
     </row>
@@ -1183,17 +1183,17 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>290.00</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>298.80</t>
+          <t>298.8</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>288.00</t>
+          <t>288.0</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1238,9 +1238,9 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>-0.94%</t>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -1950,698 +1950,698 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>313.80</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>311.50</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>318.55</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>306.40</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>12910</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>+1.42%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -2653,116 +2653,153 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G64"/>
+  <autoFilter ref="A4:G65"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-25 04:07:37</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-26 04:23:32</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>288.80</t>
+          <t>288.8</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>282.00</t>
+          <t>282.0</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1275,9 +1275,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>-0.71%</t>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>313.80</t>
+          <t>298.25</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>311.50</t>
+          <t>297.70</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>12910</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>+1.42%</t>
+          <t>14168</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>-3.60%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-26 04:23:32</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-27 04:35:05</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>285.30</t>
+          <t>285.3</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>285.30</t>
+          <t>285.3</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>285.30</t>
+          <t>285.3</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>298.25</t>
+          <t>313.80</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>297.70</t>
+          <t>311.50</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>14168</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>-3.60%</t>
+          <t>12910</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>+1.42%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-27 04:35:05</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-28 03:58:46</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -1987,698 +1987,698 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>323.05</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>298.00</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>333.45</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>313.90</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>+2.95%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -2690,116 +2690,153 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G65"/>
+  <autoFilter ref="A4:G66"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-28 03:58:46</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-29 04:09:52</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>323.05</t>
+          <t>324.55</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>298.00</t>
+          <t>314.00</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2012,710 +2012,710 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>+2.95%</t>
+          <t>+3.43%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>339.40</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>346.65</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>19666</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>+4.58%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -2727,116 +2727,153 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G66"/>
+  <autoFilter ref="A4:G67"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-29 04:09:52</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-30 03:54:40</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2061,698 +2061,698 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>326.60</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>312.80</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>342.75</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>324.35</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-3.77%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -2764,116 +2764,153 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G67"/>
+  <autoFilter ref="A4:G68"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-30 03:54:40</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-31 04:20:09</t>
         </is>
       </c>
     </row>
@@ -1289,22 +1289,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>291.10</t>
+          <t>291.1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>291.10</t>
+          <t>291.1</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>291.10</t>
+          <t>291.1</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>291.10</t>
+          <t>291.1</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>+6.90%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>326.60</t>
+          <t>325.80</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>312.80</t>
+          <t>334.25</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2086,710 +2086,710 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>-4.01%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>323.05</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>332.00</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>338.75</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>322.25</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.84%</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -2801,116 +2801,153 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G68"/>
+  <autoFilter ref="A4:G69"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-07-31 04:20:09</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-01 04:19:00</t>
         </is>
       </c>
     </row>
@@ -1326,22 +1326,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>311.20</t>
+          <t>311.2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>312.00</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>314.10</t>
+          <t>314.1</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>312.00</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -2135,698 +2135,698 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>332.10</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>325.75</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>334.40</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>320.90</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>18619</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>+2.80%</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -2838,116 +2838,153 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G69"/>
+  <autoFilter ref="A4:G70"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-01 04:19:00</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-02 04:21:21</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>324.30</t>
+          <t>324.3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>310.00</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>310.00</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1423,9 +1423,9 @@
           <t>118</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>-2.67%</t>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2140,32 +2140,32 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>332.10</t>
+          <t>313.55</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>325.75</t>
+          <t>310.35</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>334.40</t>
+          <t>316.85</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>320.90</t>
+          <t>305.05</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>18619</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>+2.80%</t>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>-2.94%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-02 04:21:21</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-03 04:27:58</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>+15.30%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2140,32 +2140,32 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>313.55</t>
+          <t>332.10</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>310.35</t>
+          <t>325.75</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>316.85</t>
+          <t>334.40</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>320.90</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>12694</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>-2.94%</t>
+          <t>18619</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>+2.80%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-03 04:27:58</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-04 04:11:04</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-04 04:11:04</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-05 03:58:38</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>18619</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -2172,234 +2172,234 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>319.50</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>332.00</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>332.65</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>317.25</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-3.79%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>307.70</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>307.50</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>311.00</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>304.00</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-3.69%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>15.13K</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
+          <t>13.83K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
+          <t>12.68K</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2409,582 +2409,656 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
+          <t>8.18K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
+          <t>11.87K</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
+          <t>10.80K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
+          <t>13.92K</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>+2.31%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>23.18K</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>-1.88%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
+          <t>2026年6月5日</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>246.5</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>249.2</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>243.3</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>26.62K</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G70"/>
+  <autoFilter ref="A4:G72"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-05 03:58:38</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-06 04:09:29</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -2214,730 +2214,730 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>307.70</t>
+          <t>324.10</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>307.50</t>
+          <t>322.55</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>311.00</t>
+          <t>326.80</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>304.00</t>
+          <t>318.80</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>-3.69%</t>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>+1.44%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>326.90</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>325.40</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>331.50</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>321.60</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>+0.86%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -2949,116 +2949,153 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G72"/>
+  <autoFilter ref="A4:G73"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-06 04:09:29</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-07 03:48:18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -2283,698 +2283,698 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>324.25</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>309.60</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>330.40</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>318.30</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.81%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -2986,116 +2986,153 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G73"/>
+  <autoFilter ref="A4:G74"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-07 03:48:18</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-08 02:53:03</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>348.00</t>
+          <t>348.0</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1497,9 +1497,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>-8.89%</t>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>324.25</t>
+          <t>321.65</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>309.60</t>
+          <t>327.00</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2308,710 +2308,710 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-1.61%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>313.65</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>305.85</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>340.50</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>322.15</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>21753</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.49%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -3023,116 +3023,153 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G74"/>
+  <autoFilter ref="A4:G75"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-08 02:53:03</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-09 03:00:51</t>
         </is>
       </c>
     </row>
@@ -1474,22 +1474,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>331.60</t>
+          <t>331.6</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>331.60</t>
+          <t>331.6</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>331.60</t>
+          <t>331.6</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>331.60</t>
+          <t>331.6</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1534,9 +1534,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>-2.22%</t>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>13986</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>313.65</t>
+          <t>335.55</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>305.85</t>
+          <t>322.15</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>340.50</t>
+          <t>342.00</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>21753</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>-2.49%</t>
+          <t>12567</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>+4.32%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-09 03:00:51</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-10 03:10:00</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1516,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>334.10</t>
+          <t>334.1</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>334.10</t>
+          <t>334.1</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>+10.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2325,32 +2325,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>335.55</t>
+          <t>313.65</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
+          <t>305.85</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>340.50</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
           <t>322.15</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>342.00</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>322.15</t>
-        </is>
-      </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>12567</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>+4.32%</t>
+          <t>21753</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>-2.49%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-10 03:10:00</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-11 03:02:48</t>
         </is>
       </c>
     </row>
@@ -1608,9 +1608,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>-3.91%</t>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>313.65</t>
+          <t>335.55</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>305.85</t>
+          <t>322.15</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>340.50</t>
+          <t>342.00</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2345,710 +2345,710 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>21753</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>-2.49%</t>
+          <t>19833</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>+4.32%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>335.20</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.20</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>338.90</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>326.75</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.10%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -3060,116 +3060,153 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G76" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G75"/>
+  <autoFilter ref="A4:G76"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-11 03:02:48</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-12 03:21:37</t>
         </is>
       </c>
     </row>
@@ -1585,22 +1585,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1645,9 +1645,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>-0.47%</t>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>335.20</t>
+          <t>332.30</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>314.20</t>
+          <t>335.00</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2382,710 +2382,710 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.97%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>312.80</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.55</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>327.55</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>312.50</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-5.87%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -3097,116 +3097,153 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G76"/>
+  <autoFilter ref="A4:G77"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-12 03:21:37</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-13 03:24:54</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -2399,730 +2399,730 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>312.80</t>
+          <t>335.75</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>314.55</t>
+          <t>333.45</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>327.55</t>
+          <t>348.80</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>312.50</t>
+          <t>332.50</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-5.87%</t>
+          <t>19712</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>+1.04%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>317.25</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>315.50</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>321.20</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>313.55</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-5.51%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
@@ -3134,116 +3134,153 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G78" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G77"/>
+  <autoFilter ref="A4:G78"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-13 03:24:54</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-14 03:22:33</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -2436,730 +2436,730 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>317.25</t>
+          <t>340.10</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>315.50</t>
+          <t>336.60</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>321.20</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>313.55</t>
+          <t>333.40</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>-5.51%</t>
+          <t>18061</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>+1.30%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>313.40</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>317.45</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>320.80</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>310.40</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-7.85%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
@@ -3171,116 +3171,153 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G78"/>
+  <autoFilter ref="A4:G79"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-14 03:22:33</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-15 02:12:06</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1622,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>341.40</t>
+          <t>341.4</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>341.40</t>
+          <t>341.4</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>341.40</t>
+          <t>341.4</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>341.40</t>
+          <t>341.4</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1682,9 +1682,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>-1.23%</t>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -2473,730 +2473,730 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>313.40</t>
+          <t>333.10</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>317.45</t>
+          <t>338.00</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>320.80</t>
+          <t>341.25</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>310.40</t>
+          <t>331.00</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-7.85%</t>
+          <t>-2.06%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>319.00</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>308.95</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>21473</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-6.33%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -3208,116 +3208,153 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G79"/>
+  <autoFilter ref="A4:G80"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-15 02:12:06</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-16 02:19:27</t>
         </is>
       </c>
     </row>
@@ -1659,22 +1659,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>337.20</t>
+          <t>337.2</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>335.00</t>
+          <t>335.0</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>335.00</t>
+          <t>335.0</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>335.00</t>
+          <t>335.0</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1719,9 +1719,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>-0.82%</t>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>312.00</t>
+          <t>338.10</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>312.00</t>
+          <t>332.15</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>340.70</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>308.95</t>
+          <t>329.05</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>21473</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>-6.33%</t>
+          <t>11817</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>+1.50%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-16 02:19:27</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-17 02:18:12</t>
         </is>
       </c>
     </row>
@@ -1756,9 +1756,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>-3.93%</t>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2510,32 +2510,32 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>338.10</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>332.15</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>340.70</t>
+          <t>319.00</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>329.05</t>
+          <t>308.95</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>11817</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>+1.50%</t>
+          <t>21473</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>-6.33%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-17 02:18:12</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-18 02:13:54</t>
         </is>
       </c>
     </row>
@@ -1733,22 +1733,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>321.30</t>
+          <t>321.3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>321.30</t>
+          <t>321.3</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>321.30</t>
+          <t>321.3</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>321.30</t>
+          <t>321.3</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2510,730 +2510,730 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>312.00</t>
+          <t>338.10</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>312.00</t>
+          <t>332.15</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>340.70</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>308.95</t>
+          <t>329.05</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>21473</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>-6.33%</t>
+          <t>11817</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>+1.50%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>317.65</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.10</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>324.90</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>313.70</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-6.05%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -3245,116 +3245,153 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G80"/>
+  <autoFilter ref="A4:G81"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-18 02:13:54</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-19 02:16:28</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -2547,730 +2547,730 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>317.65</t>
+          <t>345.10</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>314.10</t>
+          <t>338.50</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>324.90</t>
+          <t>354.00</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>313.70</t>
+          <t>338.50</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>-6.05%</t>
+          <t>14332</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>+2.07%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>331.60</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>317.50</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>333.25</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>315.05</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-3.91%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -3282,116 +3282,153 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G81"/>
+  <autoFilter ref="A4:G82"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-19 02:16:28</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-20 02:15:38</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -2584,730 +2584,730 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>331.60</t>
+          <t>363.40</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>317.50</t>
+          <t>346.25</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>333.25</t>
+          <t>364.25</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>315.05</t>
+          <t>344.90</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>-3.91%</t>
+          <t>8100</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>+5.30%</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>328.15</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>330.65</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>337.15</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>323.20</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-9.70%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
@@ -3319,116 +3319,153 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G82"/>
+  <autoFilter ref="A4:G83"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-20 02:15:38</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-21 02:22:07</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -2621,730 +2621,730 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>328.15</t>
+          <t>359.50</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>330.65</t>
+          <t>364.45</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>337.15</t>
+          <t>369.20</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>323.20</t>
+          <t>355.00</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-9.70%</t>
+          <t>-1.07%</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>328.30</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>328.15</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>332.70</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>320.50</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-8.68%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -3356,116 +3356,153 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G83"/>
+  <autoFilter ref="A4:G84"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-21 02:22:07</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-22 02:14:16</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>334.40</t>
+          <t>334.4</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1867,9 +1867,9 @@
           <t>14600</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>-0.73%</t>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -2658,730 +2658,730 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>328.30</t>
+          <t>363.60</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>328.15</t>
+          <t>359.80</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>332.70</t>
+          <t>366.10</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>320.50</t>
+          <t>351.20</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>-8.68%</t>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>+1.14%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>324.90</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>329.00</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>335.50</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>321.70</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-10.64%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -3393,116 +3393,153 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G84"/>
+  <autoFilter ref="A4:G85"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-22 02:14:16</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-23 02:22:18</t>
         </is>
       </c>
     </row>
@@ -1904,9 +1904,9 @@
           <t>12355</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>-4.61%</t>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -2695,32 +2695,32 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>324.90</t>
+          <t>358.75</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>329.00</t>
+          <t>363.75</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>335.50</t>
+          <t>370.10</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>321.70</t>
+          <t>359.00</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-10.64%</t>
+          <t>-1.33%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-23 02:22:18</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-24 02:21:12</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>324.60</t>
+          <t>324.6</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1941,9 +1941,9 @@
           <t>12910</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>-2.29%</t>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2695,32 +2695,32 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>358.75</t>
+          <t>324.90</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>363.75</t>
+          <t>329.00</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>370.10</t>
+          <t>335.50</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>359.00</t>
+          <t>321.70</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-10.64%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-24 02:21:12</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-25 02:16:32</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>309.40</t>
+          <t>309.4</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>321.30</t>
+          <t>321.3</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2695,730 +2695,730 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>324.90</t>
+          <t>358.75</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>329.00</t>
+          <t>363.75</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>335.50</t>
+          <t>370.10</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>321.70</t>
+          <t>359.00</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>301</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>-10.64%</t>
+          <t>-1.33%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>341.80</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>324.90</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>342.55</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>321.50</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-4.72%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -3430,116 +3430,153 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G85"/>
+  <autoFilter ref="A4:G86"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-25 02:16:32</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-26 02:23:19</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>313.80</t>
+          <t>313.8</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>311.50</t>
+          <t>311.5</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>306.40</t>
+          <t>306.4</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>+3.43%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2732,730 +2732,730 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>341.80</t>
+          <t>377.75</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>324.90</t>
+          <t>360.85</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>342.55</t>
+          <t>377.95</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>321.50</t>
+          <t>359.65</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>-4.72%</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>+5.30%</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>334.85</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>342.80</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>345.65</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>329.00</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-11.36%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -3467,116 +3467,153 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G86"/>
+  <autoFilter ref="A4:G87"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-26 02:23:19</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-27 10:53:20</t>
         </is>
       </c>
     </row>
@@ -2769,266 +2769,266 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>334.85</t>
+          <t>371.40</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>342.80</t>
+          <t>376.70</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>345.65</t>
+          <t>377.00</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>329.00</t>
+          <t>366.50</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-11.36%</t>
+          <t>-1.68%</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>357.60</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>367.95</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>367.95</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>356.65</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-3.72%</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>310.00</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>316.90</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>317.00</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>306.45</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-13.31%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>15.13K</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
+          <t>13.83K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
+          <t>12.68K</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3038,582 +3038,656 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
+          <t>8.18K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
+          <t>11.87K</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
+          <t>10.80K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
+          <t>13.92K</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>+2.31%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>23.18K</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>-1.88%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
+          <t>2026年6月5日</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>246.5</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>249.2</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>243.3</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>26.62K</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G87"/>
+  <autoFilter ref="A4:G89"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-27 10:53:20</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-28 12:29:04</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>314.00</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>313.90</t>
+          <t>313.9</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -2843,730 +2843,730 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>310.00</t>
+          <t>341.90</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>316.90</t>
+          <t>355.40</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>317.00</t>
+          <t>355.40</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>306.45</t>
+          <t>342.90</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-13.31%</t>
+          <t>-4.39%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>310.15</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>311.50</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.30</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>308.85</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-9.29%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -3578,116 +3578,153 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G89"/>
+  <autoFilter ref="A4:G90"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-28 12:29:04</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-29 07:38:59</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>339.40</t>
+          <t>339.4</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>328.0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>328.0</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2089,9 +2089,9 @@
           <t>16261</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>-4.01%</t>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>310.15</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>311.50</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>314.30</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>308.85</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>-9.29%</t>
+          <t>+nan%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-29 07:38:59</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-30 06:13:06</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>325.80</t>
+          <t>325.8</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2126,9 +2126,9 @@
           <t>18619</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>-0.84%</t>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -2880,22 +2880,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>312.60</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>311.50</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>316.85</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>308.70</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>+nan%</t>
+          <t>-8.57%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-30 06:13:06</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-31 06:39:00</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>332.00</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>+2.80%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>312.60</t>
+          <t>345.85</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>311.50</t>
+          <t>347.95</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>316.85</t>
+          <t>347.95</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>308.70</t>
+          <t>347.95</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>11539</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>-8.57%</t>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>+1.16%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-08-31 06:39:00</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-01 06:00:16</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>332.10</t>
+          <t>332.1</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>334.40</t>
+          <t>334.4</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>320.90</t>
+          <t>320.9</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2200,9 +2200,9 @@
           <t>17659</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>-3.79%</t>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -2912,698 +2912,698 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>343.90</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>343.60</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>344.85</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.56%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
@@ -3615,116 +3615,153 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G90"/>
+  <autoFilter ref="A4:G91"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-01 06:00:16</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-02 05:25:54</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -2949,698 +2949,698 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>342.25</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>345.00</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>345.00</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>333.00</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.48%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -3652,116 +3652,153 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G91"/>
+  <autoFilter ref="A4:G92"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-02 05:25:54</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-03 05:27:33</t>
         </is>
       </c>
     </row>
@@ -2986,698 +2986,698 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>328.40</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>333.00</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>334.00</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-4.05%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
@@ -3689,116 +3689,153 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G92"/>
+  <autoFilter ref="A4:G93"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-03 05:27:33</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-04 05:28:49</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>319.50</t>
+          <t>319.5</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>332.00</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-04 05:28:49</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-05 05:14:45</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>324.10</t>
+          <t>324.1</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>326.80</t>
+          <t>326.8</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>318.80</t>
+          <t>318.8</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -3023,234 +3023,234 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>324.35</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>325.50</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>327.45</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>320.00</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.23%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>324.25</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>325.75</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>325.75</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>325.75</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-0.03%</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>15.13K</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
+          <t>13.83K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
+          <t>12.68K</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3260,582 +3260,656 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
+          <t>8.18K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
+          <t>11.87K</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
+          <t>10.80K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
+          <t>13.92K</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>+2.31%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>23.18K</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>-1.88%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
+          <t>2026年6月5日</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>246.5</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>249.2</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>243.3</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>26.62K</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G93"/>
+  <autoFilter ref="A4:G95"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-05 05:14:45</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-06 05:28:56</t>
         </is>
       </c>
     </row>
@@ -2251,22 +2251,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>326.90</t>
+          <t>326.9</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>325.40</t>
+          <t>325.4</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>331.50</t>
+          <t>331.5</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>321.60</t>
+          <t>321.6</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2311,9 +2311,9 @@
           <t>12567</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>-1.61%</t>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3065,32 +3065,32 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>324.25</t>
+          <t>292.90</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>325.75</t>
+          <t>296.10</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>325.75</t>
+          <t>300.85</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>325.75</t>
+          <t>292.75</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-9.70%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-06 05:28:56</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-07 05:40:02</t>
         </is>
       </c>
     </row>
@@ -2293,17 +2293,17 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>327.00</t>
+          <t>327.0</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>330.40</t>
+          <t>330.4</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>318.30</t>
+          <t>318.3</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3065,32 +3065,32 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>292.90</t>
+          <t>324.25</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>296.10</t>
+          <t>325.75</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>300.85</t>
+          <t>325.75</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>292.75</t>
+          <t>325.75</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>-9.70%</t>
+          <t>-0.03%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-07 05:40:02</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-08 05:35:09</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>342.00</t>
+          <t>342.0</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2385,9 +2385,9 @@
           <t>19712</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>-0.97%</t>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-08 05:35:09</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-09 05:42:12</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -3097,698 +3097,698 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>318.45</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>313.80</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>313.80</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>313.80</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.79%</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -3800,116 +3800,153 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G95"/>
+  <autoFilter ref="A4:G96"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-09 05:42:12</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-10 05:34:36</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
@@ -3134,698 +3134,698 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>319.20</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>319.20</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>319.20</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>319.20</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -3837,116 +3837,153 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G96"/>
+  <autoFilter ref="A4:G97"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-10 05:34:36</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-11 05:36:19</t>
         </is>
       </c>
     </row>
@@ -2362,17 +2362,17 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>332.30</t>
+          <t>332.3</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>335.00</t>
+          <t>335.0</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>338.90</t>
+          <t>338.9</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -3171,698 +3171,698 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>315.30</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>315.30</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>315.30</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>315.30</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.22%</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -3874,116 +3874,153 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G97"/>
+  <autoFilter ref="A4:G98"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-11 05:36:19</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-12 05:23:30</t>
         </is>
       </c>
     </row>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>348.80</t>
+          <t>348.8</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>332.50</t>
+          <t>332.5</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3208,698 +3208,698 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>313.65</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.50</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.50</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>313.50</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.52%</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
@@ -3911,116 +3911,153 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="F99" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G98"/>
+  <autoFilter ref="A4:G99"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
